--- a/malla_tecnicos.xlsx
+++ b/malla_tecnicos.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>T1 APOYO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>DESCANSO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>COMPENSADO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1 APOYO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DESCANSO</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
